--- a/diseases/d169/2005-2009.xlsx
+++ b/diseases/d169/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -1653,9 +1647,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1940,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2381,6 @@
       <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -2837,9 +2822,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3263,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3704,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4145,6 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -4465,9 +4438,6 @@
       <c r="O27" t="n">
         <v>16</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.03343667774507392</v>
       </c>
@@ -4761,9 +4731,6 @@
       <c r="O29" t="n">
         <v>14</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.02925709302693968</v>
       </c>
@@ -5205,9 +5172,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -5649,9 +5613,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -5945,9 +5906,6 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -6241,9 +6199,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -6685,9 +6640,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -7129,9 +7081,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7573,9 +7522,6 @@
       <c r="O48" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.008332201976533707</v>
       </c>
@@ -8017,9 +7963,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8461,9 +8404,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -8905,9 +8845,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9349,9 +9286,6 @@
       <c r="O60" t="n">
         <v>42</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.08748812075360393</v>
       </c>
@@ -9793,9 +9727,6 @@
       <c r="O63" t="n">
         <v>16</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.03332880790613483</v>
       </c>
@@ -10237,9 +10168,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -10681,9 +10609,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11050,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -11569,9 +11491,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11932,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12373,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -12901,9 +12814,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13345,9 +13255,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13789,9 +13696,6 @@
       <c r="O90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -14085,9 +13989,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -14529,9 +14430,6 @@
       <c r="O95" t="n">
         <v>20</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -14973,9 +14871,6 @@
       <c r="O98" t="n">
         <v>32</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.06642019447064958</v>
       </c>
@@ -15417,9 +15312,6 @@
       <c r="O101" t="n">
         <v>4</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -15861,9 +15753,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16305,9 +16194,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -16749,9 +16635,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -17193,9 +17076,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17637,9 +17517,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18081,9 +17958,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -18525,9 +18399,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18840,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -19413,9 +19281,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -19857,9 +19722,6 @@
       <c r="O131" t="n">
         <v>49</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.101330756140649</v>
       </c>
@@ -20301,9 +20163,6 @@
       <c r="O134" t="n">
         <v>29</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.05997126383834328</v>
       </c>
@@ -20745,9 +20604,6 @@
       <c r="O137" t="n">
         <v>4</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -21189,9 +21045,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -21633,9 +21486,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22077,9 +21927,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -22521,9 +22368,6 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -22965,9 +22809,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23409,9 +23250,6 @@
       <c r="O155" t="n">
         <v>3</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -23853,9 +23691,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -24297,9 +24132,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -24741,9 +24573,6 @@
       <c r="O164" t="n">
         <v>3</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -25185,9 +25014,6 @@
       <c r="O167" t="n">
         <v>6</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -25629,9 +25455,6 @@
       <c r="O170" t="n">
         <v>6</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -26072,9 +25895,6 @@
       </c>
       <c r="O173" t="n">
         <v>7</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0.01441910973676854</v>
